--- a/7_Trimestre/Documentación/Plan_pruebas_integracion_comunidad_Inteligente.xlsx
+++ b/7_Trimestre/Documentación/Plan_pruebas_integracion_comunidad_Inteligente.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c01448a5502fa302/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{222B96C8-650B-490A-A21F-55BB0306BE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{222B96C8-650B-490A-A21F-55BB0306BE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B528E7FD-051C-41D9-9174-48A17A4DEBA3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{FE48C69B-C808-4A79-9FF3-DE3E1F7AFBDF}"/>
   </bookViews>
@@ -20,12 +20,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Hoja de Control'!$B$2:$F$34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Pruebas de Integración'!$A$1:$G$48</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="408">
   <si>
     <t>Plan de Pruebas de Integración</t>
   </si>
@@ -1672,15 +1672,366 @@
 Resultado esperado: Comportamiento o respuesta que el sistema debe presentar después de ejecutar cada paso.
 Resultados obtenidos: Las columnas correspondientes a resultados serán completadas una vez que se ejecuten las pruebas, permitiendo registrar si el comportamiento del sistema coincide con el resultado esperado y conformar así el Informe de Resultados de Pruebas de Integración .</t>
   </si>
+  <si>
+    <t>MODULO: AUDITORIA</t>
+  </si>
+  <si>
+    <t>Número</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>AU001</t>
+  </si>
+  <si>
+    <t>Frontend – API Login</t>
+  </si>
+  <si>
+    <t>Validar autenticación</t>
+  </si>
+  <si>
+    <t>Usuario administrador</t>
+  </si>
+  <si>
+    <t>AU002</t>
+  </si>
+  <si>
+    <t>Frontend – API Auditoría</t>
+  </si>
+  <si>
+    <t>Consulta auditoría</t>
+  </si>
+  <si>
+    <t>Usuario autenticado</t>
+  </si>
+  <si>
+    <t>AU003</t>
+  </si>
+  <si>
+    <t>Filtros Acción</t>
+  </si>
+  <si>
+    <t>Filtrar INSERT/UPDATE</t>
+  </si>
+  <si>
+    <t>Datos existentes</t>
+  </si>
+  <si>
+    <t>AU004</t>
+  </si>
+  <si>
+    <t>Filtros Entidad</t>
+  </si>
+  <si>
+    <t>Filtrar ocupantes/visitas</t>
+  </si>
+  <si>
+    <t>AU005</t>
+  </si>
+  <si>
+    <t>Buscador</t>
+  </si>
+  <si>
+    <t>Buscar registros</t>
+  </si>
+  <si>
+    <t>AU006</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>Ver detalle auditoría</t>
+  </si>
+  <si>
+    <t>Registros visibles</t>
+  </si>
+  <si>
+    <t>AU001 - PASOS</t>
+  </si>
+  <si>
+    <t>Ingresar al sistema</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Redirige a login</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Credenciales</t>
+  </si>
+  <si>
+    <t>Acceso permitido</t>
+  </si>
+  <si>
+    <t>POST 200</t>
+  </si>
+  <si>
+    <t>Ir a Auditoría</t>
+  </si>
+  <si>
+    <t>Click módulo</t>
+  </si>
+  <si>
+    <t>Carga vista</t>
+  </si>
+  <si>
+    <t>GET 200</t>
+  </si>
+  <si>
+    <t>Filtrar acción</t>
+  </si>
+  <si>
+    <t>INSERT</t>
+  </si>
+  <si>
+    <t>Tabla filtrada</t>
+  </si>
+  <si>
+    <t>Buscar</t>
+  </si>
+  <si>
+    <t>Texto</t>
+  </si>
+  <si>
+    <t>Resultados</t>
+  </si>
+  <si>
+    <t>MODULO: REPORTES</t>
+  </si>
+  <si>
+    <t>RE001</t>
+  </si>
+  <si>
+    <t>Validar acceso</t>
+  </si>
+  <si>
+    <t>Usuario registrado</t>
+  </si>
+  <si>
+    <t>RE002</t>
+  </si>
+  <si>
+    <t>Reportes Parqueaderos</t>
+  </si>
+  <si>
+    <t>Consulta API</t>
+  </si>
+  <si>
+    <t>RE003</t>
+  </si>
+  <si>
+    <t>Reportes Reservas</t>
+  </si>
+  <si>
+    <t>RE004</t>
+  </si>
+  <si>
+    <t>Reportes Residentes</t>
+  </si>
+  <si>
+    <t>RE005</t>
+  </si>
+  <si>
+    <t>Reportes Generales</t>
+  </si>
+  <si>
+    <t>Múltiples endpoints</t>
+  </si>
+  <si>
+    <t>Backend activo</t>
+  </si>
+  <si>
+    <t>RE006</t>
+  </si>
+  <si>
+    <t>Descarga PDF</t>
+  </si>
+  <si>
+    <t>Generar reporte</t>
+  </si>
+  <si>
+    <t>Datos disponibles</t>
+  </si>
+  <si>
+    <t>RE001 - PASOS</t>
+  </si>
+  <si>
+    <t>Login incorrecto</t>
+  </si>
+  <si>
+    <t>Contraseña mala</t>
+  </si>
+  <si>
+    <t>Error 400</t>
+  </si>
+  <si>
+    <t>Validación</t>
+  </si>
+  <si>
+    <t>Login correcto</t>
+  </si>
+  <si>
+    <t>Acceso</t>
+  </si>
+  <si>
+    <t>Ir a Reportes</t>
+  </si>
+  <si>
+    <t>Click</t>
+  </si>
+  <si>
+    <t>Consultar</t>
+  </si>
+  <si>
+    <t>Fechas</t>
+  </si>
+  <si>
+    <t>Datos</t>
+  </si>
+  <si>
+    <t>Descargar PDF</t>
+  </si>
+  <si>
+    <t>Archivo descargado</t>
+  </si>
+  <si>
+    <t>MODULO: PARQUEADEROS</t>
+  </si>
+  <si>
+    <t>PA001</t>
+  </si>
+  <si>
+    <t>Usuario válido</t>
+  </si>
+  <si>
+    <t>PA002</t>
+  </si>
+  <si>
+    <t>Consulta</t>
+  </si>
+  <si>
+    <t>GET parqueaderos</t>
+  </si>
+  <si>
+    <t>PA003</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Cambiar estado</t>
+  </si>
+  <si>
+    <t>Registros existentes</t>
+  </si>
+  <si>
+    <t>PA004</t>
+  </si>
+  <si>
+    <t>Actualización</t>
+  </si>
+  <si>
+    <t>Refrescar lista</t>
+  </si>
+  <si>
+    <t>Cambio realizado</t>
+  </si>
+  <si>
+    <t>PA001 - PASOS</t>
+  </si>
+  <si>
+    <t>Ir a parqueaderos</t>
+  </si>
+  <si>
+    <t>Vista cargada</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Actualiza</t>
+  </si>
+  <si>
+    <t>PATCH 200</t>
+  </si>
+  <si>
+    <t>Validar</t>
+  </si>
+  <si>
+    <t>Recarga</t>
+  </si>
+  <si>
+    <t>Datos actualizados</t>
+  </si>
+  <si>
+    <t>MODULO: LOG ERRORES</t>
+  </si>
+  <si>
+    <t>LE001</t>
+  </si>
+  <si>
+    <t>LE002</t>
+  </si>
+  <si>
+    <t>Consulta Logs</t>
+  </si>
+  <si>
+    <t>GET logs</t>
+  </si>
+  <si>
+    <t>LE003</t>
+  </si>
+  <si>
+    <t>Filtro Nivel</t>
+  </si>
+  <si>
+    <t>ERROR/WARN/INFO</t>
+  </si>
+  <si>
+    <t>LE004</t>
+  </si>
+  <si>
+    <t>Resumen</t>
+  </si>
+  <si>
+    <t>Ver resumen</t>
+  </si>
+  <si>
+    <t>LE001 - PASOS</t>
+  </si>
+  <si>
+    <t>Ir a logs</t>
+  </si>
+  <si>
+    <t>limite</t>
+  </si>
+  <si>
+    <t>Filtrar</t>
+  </si>
+  <si>
+    <t>Nivel</t>
+  </si>
+  <si>
+    <t>Lista filtrada</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; &quot;[$€];[Red]&quot;-&quot;#,##0.00&quot; &quot;[$€]"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; &quot;[$€];[Red]&quot;-&quot;#,##0.00&quot; &quot;[$€]"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1914,8 +2265,24 @@
       <color theme="1"/>
       <name val="Arial1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial1"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2078,8 +2445,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="39">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -2595,6 +2968,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2646,11 +3028,11 @@
       <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="6"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2680,7 +3062,7 @@
     <xf numFmtId="49" fontId="24" fillId="24" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2720,56 +3102,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="10" xfId="41" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="10" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="10" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="10" xfId="41" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2787,62 +3136,118 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="47" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="47" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="35" xfId="41" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="31" xfId="41" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="36" xfId="41" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="47" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="25" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="47" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="35" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="31" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="36" xfId="41" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="34" xfId="47" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="48">
@@ -3356,43 +3761,43 @@
       <c r="F2"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
     </row>
     <row r="7" spans="2:8" ht="30">
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="69"/>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="2:8" ht="30">
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
     </row>
     <row r="12" spans="2:8">
       <c r="F12" s="3"/>
     </row>
     <row r="15" spans="2:8" ht="30">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
     </row>
     <row r="17" spans="2:16" ht="14.4" thickBot="1">
       <c r="B17"/>
@@ -3403,54 +3808,54 @@
       <c r="B18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
     </row>
     <row r="19" spans="2:16" ht="17.399999999999999">
       <c r="B19" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
     </row>
     <row r="20" spans="2:16" ht="17.399999999999999">
       <c r="B20" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
     </row>
     <row r="21" spans="2:16" ht="19.8" customHeight="1" thickBot="1">
       <c r="B21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
     </row>
     <row r="22" spans="2:16" ht="19.8" customHeight="1" thickTop="1">
       <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="41"/>
+      <c r="D22" s="78"/>
       <c r="E22" s="8" t="s">
         <v>8</v>
       </c>
@@ -3462,8 +3867,8 @@
       <c r="B23" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
       <c r="E23" s="10" t="s">
         <v>11</v>
       </c>
@@ -3473,8 +3878,8 @@
     </row>
     <row r="24" spans="2:16" ht="19.8" customHeight="1" thickBot="1">
       <c r="B24" s="11"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
       <c r="E24" s="12" t="s">
         <v>12</v>
       </c>
@@ -3504,10 +3909,10 @@
       <c r="C28" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="44"/>
+      <c r="E28" s="73"/>
       <c r="F28" s="18" t="s">
         <v>19</v>
       </c>
@@ -3519,10 +3924,10 @@
       <c r="C29" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="45"/>
+      <c r="E29" s="74"/>
       <c r="F29" s="21" t="s">
         <v>34</v>
       </c>
@@ -3530,15 +3935,15 @@
     <row r="30" spans="2:16" ht="25.5" customHeight="1">
       <c r="B30" s="22"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="2:16" ht="25.5" customHeight="1">
       <c r="B31" s="22"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
       <c r="F31" s="9"/>
     </row>
     <row r="32" spans="2:16" ht="25.5" customHeight="1">
@@ -3685,7 +4090,7 @@
     </row>
     <row r="53" spans="1:256" ht="19.8" customHeight="1">
       <c r="A53" s="24"/>
-      <c r="B53" s="32"/>
+      <c r="B53" s="30"/>
       <c r="C53" s="23"/>
       <c r="D53" s="23"/>
       <c r="G53" s="23"/>
@@ -3705,7 +4110,7 @@
     </row>
     <row r="55" spans="1:256" ht="19.8" customHeight="1">
       <c r="A55" s="28"/>
-      <c r="B55" s="32"/>
+      <c r="B55" s="30"/>
       <c r="C55" s="23"/>
       <c r="D55" s="23"/>
       <c r="F55" s="24"/>
@@ -3724,7 +4129,7 @@
     </row>
     <row r="57" spans="1:256" ht="19.8" customHeight="1">
       <c r="A57" s="28"/>
-      <c r="B57" s="33"/>
+      <c r="B57" s="32"/>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
       <c r="E57" s="28"/>
@@ -3744,7 +4149,7 @@
     </row>
     <row r="59" spans="1:256" ht="19.8" customHeight="1">
       <c r="A59" s="28"/>
-      <c r="B59" s="33"/>
+      <c r="B59" s="32"/>
       <c r="C59" s="23"/>
       <c r="D59" s="23"/>
       <c r="G59" s="23"/>
@@ -3761,7 +4166,7 @@
     </row>
     <row r="61" spans="1:256" ht="19.8" customHeight="1">
       <c r="A61" s="28"/>
-      <c r="B61" s="33"/>
+      <c r="B61" s="32"/>
       <c r="C61" s="23"/>
       <c r="D61" s="23"/>
       <c r="G61" s="25"/>
@@ -3779,7 +4184,7 @@
     </row>
     <row r="63" spans="1:256" ht="19.8" customHeight="1">
       <c r="A63" s="28"/>
-      <c r="B63" s="33"/>
+      <c r="B63" s="32"/>
       <c r="C63" s="23"/>
       <c r="D63" s="23"/>
       <c r="G63" s="23"/>
@@ -3797,7 +4202,7 @@
     </row>
     <row r="65" spans="1:12" ht="19.8" customHeight="1">
       <c r="A65" s="28"/>
-      <c r="B65" s="33"/>
+      <c r="B65" s="32"/>
       <c r="C65" s="23"/>
       <c r="D65" s="23"/>
       <c r="G65" s="23"/>
@@ -3814,7 +4219,7 @@
     </row>
     <row r="67" spans="1:12" ht="19.8" customHeight="1">
       <c r="A67" s="28"/>
-      <c r="B67" s="33"/>
+      <c r="B67" s="32"/>
       <c r="C67" s="23"/>
       <c r="D67" s="23"/>
     </row>
@@ -3826,7 +4231,7 @@
     </row>
     <row r="69" spans="1:12" ht="19.8" customHeight="1">
       <c r="A69" s="28"/>
-      <c r="B69" s="33"/>
+      <c r="B69" s="32"/>
       <c r="C69" s="23"/>
       <c r="D69" s="23"/>
     </row>
@@ -3838,7 +4243,7 @@
     </row>
     <row r="71" spans="1:12" ht="19.8" customHeight="1">
       <c r="A71" s="28"/>
-      <c r="B71" s="33"/>
+      <c r="B71" s="32"/>
       <c r="C71" s="23"/>
       <c r="D71" s="23"/>
     </row>
@@ -3850,7 +4255,7 @@
     </row>
     <row r="73" spans="1:12" ht="19.8" customHeight="1">
       <c r="A73" s="28"/>
-      <c r="B73" s="33"/>
+      <c r="B73" s="32"/>
       <c r="C73" s="23"/>
       <c r="D73" s="23"/>
     </row>
@@ -3862,7 +4267,7 @@
     </row>
     <row r="75" spans="1:12" ht="19.8" customHeight="1">
       <c r="A75" s="28"/>
-      <c r="B75" s="33"/>
+      <c r="B75" s="32"/>
       <c r="C75" s="23"/>
       <c r="D75" s="23"/>
     </row>
@@ -3872,7 +4277,7 @@
       <c r="D76" s="23"/>
     </row>
     <row r="77" spans="1:12" ht="19.8" customHeight="1">
-      <c r="B77" s="33"/>
+      <c r="B77" s="32"/>
       <c r="C77" s="23"/>
       <c r="D77" s="23"/>
     </row>
@@ -3882,7 +4287,7 @@
       <c r="D78" s="23"/>
     </row>
     <row r="79" spans="1:12" ht="19.8" customHeight="1">
-      <c r="B79" s="33"/>
+      <c r="B79" s="32"/>
       <c r="C79" s="23"/>
       <c r="D79" s="23"/>
     </row>
@@ -3890,13 +4295,13 @@
       <c r="B80" s="23"/>
       <c r="C80" s="23"/>
       <c r="D80" s="23"/>
-      <c r="J80" s="34"/>
+      <c r="J80" s="33"/>
     </row>
     <row r="81" spans="2:10">
-      <c r="B81" s="33"/>
+      <c r="B81" s="32"/>
       <c r="C81" s="23"/>
       <c r="D81" s="23"/>
-      <c r="J81" s="34"/>
+      <c r="J81" s="33"/>
     </row>
     <row r="82" spans="2:10">
       <c r="B82" s="25"/>
@@ -3909,16 +4314,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="F5:H5"/>
@@ -3926,6 +4321,16 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="3.9763779527559058E-2" bottom="3.9763779527559058E-2" header="0" footer="0"/>
@@ -3936,7 +4341,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D584C9F-B785-4EDF-8D2D-734D2D8A8AC0}">
-  <dimension ref="A5:IX159"/>
+  <dimension ref="A5:IX230"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -3944,7 +4349,7 @@
     <col min="3" max="3" width="29.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.69921875" style="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.296875" style="1" customWidth="1"/>
     <col min="7" max="7" width="39.296875" style="1" customWidth="1"/>
     <col min="8" max="10" width="20.796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="32.09765625" style="1" customWidth="1"/>
@@ -3955,30 +4360,30 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:12">
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
     </row>
     <row r="6" spans="2:12">
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
     </row>
     <row r="7" spans="2:12" ht="30">
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
     </row>
     <row r="8" spans="2:12" ht="30">
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -3990,40 +4395,40 @@
       <c r="E12"/>
     </row>
     <row r="13" spans="2:12" ht="111.9" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B13" s="82" t="s">
+      <c r="B13" s="70" t="s">
         <v>290</v>
       </c>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
     </row>
     <row r="14" spans="2:12" ht="19.8" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
       <c r="K14"/>
       <c r="L14"/>
     </row>
     <row r="15" spans="2:12" ht="19.8" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
     </row>
     <row r="16" spans="2:12" ht="19.8" customHeight="1" thickTop="1">
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
     </row>
     <row r="17" spans="1:258" ht="19.8" customHeight="1">
       <c r="A17" s="28"/>
@@ -4031,32 +4436,32 @@
         <v>89</v>
       </c>
       <c r="C17" s="65"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47"/>
+      <c r="G17" s="47"/>
     </row>
     <row r="18" spans="1:258" ht="19.8" customHeight="1">
-      <c r="B18" s="48"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
     </row>
     <row r="19" spans="1:258" ht="39" customHeight="1">
       <c r="A19" s="28"/>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="D19" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="34"/>
+      <c r="F19" s="33"/>
       <c r="IS19"/>
       <c r="IT19"/>
       <c r="IU19"/>
@@ -4066,19 +4471,19 @@
     </row>
     <row r="20" spans="1:258" ht="131.4" customHeight="1">
       <c r="A20" s="28"/>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="F20" s="34"/>
+      <c r="F20" s="33"/>
       <c r="IS20"/>
       <c r="IT20"/>
       <c r="IU20"/>
@@ -4088,19 +4493,19 @@
     </row>
     <row r="21" spans="1:258" ht="75" customHeight="1">
       <c r="A21" s="28"/>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="54" t="s">
+      <c r="E21" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="34"/>
+      <c r="F21" s="33"/>
       <c r="IS21"/>
       <c r="IT21"/>
       <c r="IU21"/>
@@ -4110,19 +4515,19 @@
     </row>
     <row r="22" spans="1:258" ht="75" customHeight="1">
       <c r="A22" s="28"/>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="54" t="s">
+      <c r="C22" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="54" t="s">
+      <c r="D22" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="54" t="s">
+      <c r="E22" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="46"/>
+      <c r="F22" s="34"/>
       <c r="IS22"/>
       <c r="IT22"/>
       <c r="IU22"/>
@@ -4132,19 +4537,19 @@
     </row>
     <row r="23" spans="1:258" ht="64.8" customHeight="1">
       <c r="A23" s="28"/>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="54" t="s">
+      <c r="D23" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="54" t="s">
+      <c r="E23" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="46"/>
+      <c r="F23" s="34"/>
       <c r="IS23"/>
       <c r="IT23"/>
       <c r="IU23"/>
@@ -4154,19 +4559,19 @@
     </row>
     <row r="24" spans="1:258" ht="57.6" customHeight="1">
       <c r="A24" s="28"/>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D24" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="54" t="s">
+      <c r="E24" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="46"/>
+      <c r="F24" s="34"/>
       <c r="IS24"/>
       <c r="IT24"/>
       <c r="IU24"/>
@@ -4176,19 +4581,19 @@
     </row>
     <row r="25" spans="1:258" ht="64.2" customHeight="1">
       <c r="A25" s="28"/>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="54" t="s">
+      <c r="C25" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="54" t="s">
+      <c r="D25" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="54" t="s">
+      <c r="E25" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="46"/>
+      <c r="F25" s="34"/>
       <c r="IS25"/>
       <c r="IT25"/>
       <c r="IU25"/>
@@ -4197,11 +4602,11 @@
       <c r="IX25"/>
     </row>
     <row r="26" spans="1:258" ht="30" customHeight="1">
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="55"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="42"/>
       <c r="IS26"/>
       <c r="IT26"/>
       <c r="IU26"/>
@@ -4210,11 +4615,11 @@
       <c r="IX26"/>
     </row>
     <row r="27" spans="1:258" ht="30" customHeight="1">
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="55"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="42"/>
       <c r="IS27"/>
       <c r="IT27"/>
       <c r="IU27"/>
@@ -4223,219 +4628,219 @@
       <c r="IX27"/>
     </row>
     <row r="28" spans="1:258" ht="19.8" customHeight="1" thickBot="1">
-      <c r="B28" s="46"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
     </row>
     <row r="29" spans="1:258" ht="19.8" customHeight="1" thickTop="1">
       <c r="B29" s="59" t="s">
         <v>37</v>
       </c>
       <c r="C29" s="59"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
     </row>
     <row r="30" spans="1:258" ht="19.8" customHeight="1">
       <c r="A30" s="28"/>
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="73" t="s">
+      <c r="C30" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="73" t="s">
+      <c r="D30" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="73" t="s">
+      <c r="E30" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="F30" s="73" t="s">
+      <c r="F30" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="73" t="s">
+      <c r="G30" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="H30" s="34"/>
+      <c r="H30" s="33"/>
     </row>
     <row r="31" spans="1:258" ht="38.4" customHeight="1">
       <c r="A31" s="28"/>
-      <c r="B31" s="51">
+      <c r="B31" s="38">
         <v>1</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="51" t="s">
+      <c r="F31" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="H31" s="34"/>
+      <c r="H31" s="33"/>
     </row>
     <row r="32" spans="1:258" ht="37.200000000000003" customHeight="1">
       <c r="A32" s="28"/>
-      <c r="B32" s="58">
+      <c r="B32" s="67">
         <v>2</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="67" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="51" t="s">
+      <c r="D32" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="F32" s="58" t="s">
+      <c r="F32" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="G32" s="58" t="s">
+      <c r="G32" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="H32" s="34"/>
+      <c r="H32" s="33"/>
     </row>
     <row r="33" spans="1:258" ht="36" customHeight="1">
       <c r="A33" s="28"/>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="51" t="s">
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="34"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="33"/>
     </row>
     <row r="34" spans="1:258" ht="36" customHeight="1">
       <c r="A34" s="28"/>
-      <c r="B34" s="51">
+      <c r="B34" s="38">
         <v>3</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="51" t="s">
+      <c r="E34" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="F34" s="51" t="s">
+      <c r="F34" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="51" t="s">
+      <c r="G34" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="H34" s="34"/>
+      <c r="H34" s="33"/>
     </row>
     <row r="35" spans="1:258" ht="61.8" customHeight="1">
       <c r="A35" s="28"/>
-      <c r="B35" s="51">
+      <c r="B35" s="38">
         <v>4</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E35" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F35" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G35" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="34"/>
+      <c r="H35" s="33"/>
     </row>
     <row r="36" spans="1:258" ht="36.6" customHeight="1">
       <c r="A36" s="28"/>
-      <c r="B36" s="58">
+      <c r="B36" s="67">
         <v>5</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="F36" s="58" t="s">
+      <c r="F36" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="G36" s="58" t="s">
+      <c r="G36" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="H36" s="34"/>
+      <c r="H36" s="33"/>
     </row>
     <row r="37" spans="1:258" ht="36.6" customHeight="1">
       <c r="A37" s="28"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="34"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="33"/>
     </row>
     <row r="38" spans="1:258" ht="36.6" customHeight="1">
       <c r="A38" s="28"/>
-      <c r="B38" s="51">
+      <c r="B38" s="38">
         <v>6</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="51" t="s">
+      <c r="D38" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="E38" s="51" t="s">
+      <c r="E38" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="F38" s="51" t="s">
+      <c r="F38" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="G38" s="51" t="s">
+      <c r="G38" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="34"/>
+      <c r="H38" s="33"/>
     </row>
     <row r="39" spans="1:258" ht="36.6" customHeight="1">
       <c r="A39" s="28"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="34"/>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="33"/>
     </row>
     <row r="40" spans="1:258" ht="19.8" customHeight="1">
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
     </row>
     <row r="41" spans="1:258" ht="19.8" customHeight="1">
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
       <c r="IS41"/>
       <c r="IT41"/>
       <c r="IU41"/>
@@ -4445,11 +4850,11 @@
     </row>
     <row r="42" spans="1:258" ht="19.8" customHeight="1">
       <c r="A42" s="28"/>
-      <c r="B42" s="72" t="s">
+      <c r="B42" s="66" t="s">
         <v>132</v>
       </c>
-      <c r="C42" s="72"/>
-      <c r="D42" s="34"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="33"/>
       <c r="IS42"/>
       <c r="IT42"/>
       <c r="IU42"/>
@@ -4458,10 +4863,10 @@
       <c r="IX42"/>
     </row>
     <row r="43" spans="1:258" ht="19.8" customHeight="1">
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="39"/>
       <c r="IS43"/>
       <c r="IT43"/>
       <c r="IU43"/>
@@ -4471,19 +4876,19 @@
     </row>
     <row r="44" spans="1:258" ht="27.6" customHeight="1">
       <c r="A44" s="28"/>
-      <c r="B44" s="56" t="s">
+      <c r="B44" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="56" t="s">
+      <c r="C44" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="56" t="s">
+      <c r="D44" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="56" t="s">
+      <c r="E44" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F44" s="34"/>
+      <c r="F44" s="33"/>
       <c r="IS44"/>
       <c r="IT44"/>
       <c r="IU44"/>
@@ -4493,19 +4898,19 @@
     </row>
     <row r="45" spans="1:258" ht="75.599999999999994" customHeight="1">
       <c r="A45" s="28"/>
-      <c r="B45" s="54" t="s">
+      <c r="B45" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="54" t="s">
+      <c r="C45" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D45" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="E45" s="61" t="s">
+      <c r="E45" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="F45" s="34"/>
+      <c r="F45" s="33"/>
       <c r="IS45"/>
       <c r="IT45"/>
       <c r="IU45"/>
@@ -4515,19 +4920,19 @@
     </row>
     <row r="46" spans="1:258" ht="48" customHeight="1">
       <c r="A46" s="28"/>
-      <c r="B46" s="54" t="s">
+      <c r="B46" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="C46" s="54" t="s">
+      <c r="C46" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="D46" s="54" t="s">
+      <c r="D46" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="E46" s="54" t="s">
+      <c r="E46" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="34"/>
+      <c r="F46" s="33"/>
       <c r="IS46"/>
       <c r="IT46"/>
       <c r="IU46"/>
@@ -4537,19 +4942,19 @@
     </row>
     <row r="47" spans="1:258" ht="61.2" customHeight="1">
       <c r="A47" s="28"/>
-      <c r="B47" s="54" t="s">
+      <c r="B47" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="54" t="s">
+      <c r="C47" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="54" t="s">
+      <c r="D47" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="E47" s="54" t="s">
+      <c r="E47" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="F47" s="34"/>
+      <c r="F47" s="33"/>
       <c r="IS47"/>
       <c r="IT47"/>
       <c r="IU47"/>
@@ -4559,19 +4964,19 @@
     </row>
     <row r="48" spans="1:258" ht="39" customHeight="1">
       <c r="A48" s="28"/>
-      <c r="B48" s="54" t="s">
+      <c r="B48" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="54" t="s">
+      <c r="C48" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="D48" s="54" t="s">
+      <c r="D48" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="54" t="s">
+      <c r="E48" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="F48" s="34"/>
+      <c r="F48" s="33"/>
       <c r="IS48"/>
       <c r="IT48"/>
       <c r="IU48"/>
@@ -4581,19 +4986,19 @@
     </row>
     <row r="49" spans="1:258" ht="41.4" customHeight="1">
       <c r="A49" s="28"/>
-      <c r="B49" s="54" t="s">
+      <c r="B49" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="54" t="s">
+      <c r="C49" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="54" t="s">
+      <c r="D49" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="E49" s="54" t="s">
+      <c r="E49" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="F49" s="34"/>
+      <c r="F49" s="33"/>
       <c r="IS49"/>
       <c r="IT49"/>
       <c r="IU49"/>
@@ -4603,19 +5008,19 @@
     </row>
     <row r="50" spans="1:258" ht="54.6" customHeight="1">
       <c r="A50" s="28"/>
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="54" t="s">
+      <c r="C50" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="54" t="s">
+      <c r="D50" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="E50" s="54" t="s">
+      <c r="E50" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="F50" s="34"/>
+      <c r="F50" s="33"/>
       <c r="IS50"/>
       <c r="IT50"/>
       <c r="IU50"/>
@@ -4625,10 +5030,10 @@
     </row>
     <row r="51" spans="1:258" ht="19.8" customHeight="1" thickBot="1">
       <c r="A51" s="28"/>
-      <c r="B51" s="48"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
       <c r="IS51"/>
       <c r="IT51"/>
       <c r="IU51"/>
@@ -4647,315 +5052,315 @@
     </row>
     <row r="53" spans="1:258" ht="19.8" customHeight="1">
       <c r="A53" s="28"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="67"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
     </row>
     <row r="54" spans="1:258" ht="19.8" customHeight="1">
       <c r="A54" s="28"/>
-      <c r="B54" s="56" t="s">
+      <c r="B54" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C54" s="56" t="s">
+      <c r="C54" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D54" s="56" t="s">
+      <c r="D54" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E54" s="56" t="s">
+      <c r="E54" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="F54" s="56" t="s">
+      <c r="F54" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="G54" s="56" t="s">
+      <c r="G54" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="H54" s="34"/>
+      <c r="H54" s="33"/>
     </row>
     <row r="55" spans="1:258" ht="55.2" customHeight="1">
       <c r="A55" s="28"/>
-      <c r="B55" s="54">
+      <c r="B55" s="41">
         <v>1</v>
       </c>
-      <c r="C55" s="54" t="s">
+      <c r="C55" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="61" t="s">
+      <c r="D55" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="E55" s="54" t="s">
+      <c r="E55" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="F55" s="54" t="s">
+      <c r="F55" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G55" s="54" t="s">
+      <c r="G55" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="H55" s="34"/>
+      <c r="H55" s="33"/>
     </row>
     <row r="56" spans="1:258" ht="42" customHeight="1">
       <c r="A56" s="28"/>
-      <c r="B56" s="54">
+      <c r="B56" s="41">
         <v>2</v>
       </c>
-      <c r="C56" s="54" t="s">
+      <c r="C56" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="D56" s="54" t="s">
+      <c r="D56" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="E56" s="54" t="s">
+      <c r="E56" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="F56" s="54" t="s">
+      <c r="F56" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G56" s="54" t="s">
+      <c r="G56" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="H56" s="34"/>
+      <c r="H56" s="33"/>
     </row>
     <row r="57" spans="1:258" ht="40.200000000000003" customHeight="1">
       <c r="A57" s="28"/>
-      <c r="B57" s="54">
+      <c r="B57" s="41">
         <v>3</v>
       </c>
-      <c r="C57" s="54" t="s">
+      <c r="C57" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="54" t="s">
+      <c r="D57" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="E57" s="54" t="s">
+      <c r="E57" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="F57" s="54" t="s">
+      <c r="F57" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G57" s="54" t="s">
+      <c r="G57" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="H57" s="34"/>
+      <c r="H57" s="33"/>
     </row>
     <row r="58" spans="1:258" ht="43.2" customHeight="1">
       <c r="A58" s="28"/>
-      <c r="B58" s="54">
+      <c r="B58" s="41">
         <v>4</v>
       </c>
-      <c r="C58" s="54" t="s">
+      <c r="C58" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D58" s="54" t="s">
+      <c r="D58" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="E58" s="54" t="s">
+      <c r="E58" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="F58" s="54" t="s">
+      <c r="F58" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G58" s="54" t="s">
+      <c r="G58" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="H58" s="34"/>
+      <c r="H58" s="33"/>
     </row>
     <row r="59" spans="1:258" ht="40.799999999999997" customHeight="1">
       <c r="A59" s="28"/>
-      <c r="B59" s="54">
+      <c r="B59" s="41">
         <v>5</v>
       </c>
-      <c r="C59" s="54" t="s">
+      <c r="C59" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="D59" s="61" t="s">
+      <c r="D59" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="E59" s="54" t="s">
+      <c r="E59" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="F59" s="54" t="s">
+      <c r="F59" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G59" s="54" t="s">
+      <c r="G59" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="H59" s="34"/>
+      <c r="H59" s="33"/>
     </row>
     <row r="60" spans="1:258" ht="55.2" customHeight="1">
       <c r="A60" s="28"/>
-      <c r="B60" s="54">
+      <c r="B60" s="41">
         <v>6</v>
       </c>
-      <c r="C60" s="54" t="s">
+      <c r="C60" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="D60" s="54" t="s">
+      <c r="D60" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="E60" s="54" t="s">
+      <c r="E60" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="F60" s="54" t="s">
+      <c r="F60" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G60" s="54" t="s">
+      <c r="G60" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="H60" s="34"/>
+      <c r="H60" s="33"/>
     </row>
     <row r="61" spans="1:258" ht="19.8" customHeight="1">
-      <c r="B61" s="76"/>
-      <c r="C61" s="77"/>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
+      <c r="B61" s="55"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="51"/>
+      <c r="E61" s="51"/>
+      <c r="F61" s="36"/>
+      <c r="G61" s="36"/>
     </row>
     <row r="62" spans="1:258" ht="19.8" customHeight="1">
       <c r="A62" s="28"/>
-      <c r="B62" s="71" t="s">
+      <c r="B62" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="C62" s="71"/>
-      <c r="D62" s="75"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="54"/>
       <c r="E62" s="23"/>
     </row>
     <row r="63" spans="1:258">
-      <c r="B63" s="68"/>
-      <c r="C63" s="69"/>
+      <c r="B63" s="50"/>
+      <c r="C63" s="51"/>
       <c r="D63" s="23"/>
       <c r="E63" s="23"/>
     </row>
     <row r="64" spans="1:258">
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
     </row>
     <row r="65" spans="1:8" ht="27.6">
       <c r="A65" s="28"/>
-      <c r="B65" s="56" t="s">
+      <c r="B65" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="56" t="s">
+      <c r="C65" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="56" t="s">
+      <c r="D65" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E65" s="56" t="s">
+      <c r="E65" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F65" s="34"/>
+      <c r="F65" s="33"/>
     </row>
     <row r="66" spans="1:8" ht="55.2">
       <c r="A66" s="28"/>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="54" t="s">
+      <c r="C66" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="54" t="s">
+      <c r="D66" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="E66" s="61" t="s">
+      <c r="E66" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="F66" s="34"/>
+      <c r="F66" s="33"/>
     </row>
     <row r="67" spans="1:8" ht="69">
       <c r="A67" s="28"/>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="54" t="s">
+      <c r="C67" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="D67" s="54" t="s">
+      <c r="D67" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="E67" s="54" t="s">
+      <c r="E67" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="F67" s="34"/>
+      <c r="F67" s="33"/>
     </row>
     <row r="68" spans="1:8" ht="55.2">
       <c r="A68" s="28"/>
-      <c r="B68" s="54" t="s">
+      <c r="B68" s="41" t="s">
         <v>146</v>
       </c>
-      <c r="C68" s="54" t="s">
+      <c r="C68" s="41" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="54" t="s">
+      <c r="D68" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="E68" s="54" t="s">
+      <c r="E68" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F68" s="34"/>
+      <c r="F68" s="33"/>
     </row>
     <row r="69" spans="1:8" ht="69">
       <c r="A69" s="28"/>
-      <c r="B69" s="54" t="s">
+      <c r="B69" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="C69" s="54" t="s">
+      <c r="C69" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D69" s="54" t="s">
+      <c r="D69" s="41" t="s">
         <v>152</v>
       </c>
-      <c r="E69" s="54" t="s">
+      <c r="E69" s="41" t="s">
         <v>153</v>
       </c>
-      <c r="F69" s="34"/>
+      <c r="F69" s="33"/>
     </row>
     <row r="70" spans="1:8" ht="55.2">
       <c r="A70" s="28"/>
-      <c r="B70" s="54" t="s">
+      <c r="B70" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="C70" s="54" t="s">
+      <c r="C70" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="D70" s="54" t="s">
+      <c r="D70" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="E70" s="54" t="s">
+      <c r="E70" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="F70" s="34"/>
+      <c r="F70" s="33"/>
     </row>
     <row r="71" spans="1:8" ht="55.2">
       <c r="A71" s="28"/>
-      <c r="B71" s="54" t="s">
+      <c r="B71" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="C71" s="54" t="s">
+      <c r="C71" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="D71" s="54" t="s">
+      <c r="D71" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="E71" s="54" t="s">
+      <c r="E71" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="F71" s="34"/>
+      <c r="F71" s="33"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="28"/>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
-      <c r="D72" s="74"/>
-      <c r="E72" s="74"/>
-      <c r="F72" s="34"/>
+      <c r="B72" s="53"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="33"/>
     </row>
     <row r="73" spans="1:8" ht="14.4" thickBot="1"/>
     <row r="74" spans="1:8" ht="17.399999999999999" thickTop="1">
@@ -4965,374 +5370,374 @@
       <c r="C74" s="59"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="39"/>
+      <c r="D75" s="39"/>
+      <c r="E75" s="39"/>
+      <c r="F75" s="39"/>
+      <c r="G75" s="39"/>
     </row>
     <row r="76" spans="1:8" ht="27.6">
       <c r="A76" s="28"/>
-      <c r="B76" s="53" t="s">
+      <c r="B76" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C76" s="53" t="s">
+      <c r="C76" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D76" s="53" t="s">
+      <c r="D76" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="E76" s="53" t="s">
+      <c r="E76" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F76" s="53" t="s">
+      <c r="F76" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="G76" s="53" t="s">
+      <c r="G76" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="H76" s="34"/>
+      <c r="H76" s="33"/>
     </row>
     <row r="77" spans="1:8" ht="40.200000000000003" customHeight="1">
       <c r="A77" s="28"/>
-      <c r="B77" s="54">
+      <c r="B77" s="41">
         <v>1</v>
       </c>
-      <c r="C77" s="54" t="s">
+      <c r="C77" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D77" s="61" t="s">
+      <c r="D77" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="E77" s="54" t="s">
+      <c r="E77" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="F77" s="54" t="s">
+      <c r="F77" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G77" s="54" t="s">
+      <c r="G77" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="H77" s="34"/>
+      <c r="H77" s="33"/>
     </row>
     <row r="78" spans="1:8" ht="24" customHeight="1">
       <c r="A78" s="28"/>
-      <c r="B78" s="62">
+      <c r="B78" s="58">
         <v>2</v>
       </c>
-      <c r="C78" s="62" t="s">
+      <c r="C78" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D78" s="54" t="s">
+      <c r="D78" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E78" s="62" t="s">
+      <c r="E78" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="F78" s="62" t="s">
+      <c r="F78" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G78" s="62" t="s">
+      <c r="G78" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="H78" s="34"/>
+      <c r="H78" s="33"/>
     </row>
     <row r="79" spans="1:8" ht="27.6" customHeight="1">
       <c r="A79" s="28"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="54" t="s">
+      <c r="B79" s="58"/>
+      <c r="C79" s="58"/>
+      <c r="D79" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E79" s="62"/>
-      <c r="F79" s="62"/>
-      <c r="G79" s="62"/>
-      <c r="H79" s="34"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="58"/>
+      <c r="G79" s="58"/>
+      <c r="H79" s="33"/>
     </row>
     <row r="80" spans="1:8" ht="39" customHeight="1">
       <c r="A80" s="28"/>
-      <c r="B80" s="54">
+      <c r="B80" s="41">
         <v>3</v>
       </c>
-      <c r="C80" s="54" t="s">
+      <c r="C80" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="D80" s="54" t="s">
+      <c r="D80" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="E80" s="54" t="s">
+      <c r="E80" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="F80" s="54" t="s">
+      <c r="F80" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G80" s="54" t="s">
+      <c r="G80" s="41" t="s">
         <v>187</v>
       </c>
-      <c r="H80" s="34"/>
+      <c r="H80" s="33"/>
     </row>
     <row r="81" spans="1:8" ht="35.4" customHeight="1">
       <c r="A81" s="28"/>
-      <c r="B81" s="54">
+      <c r="B81" s="41">
         <v>4</v>
       </c>
-      <c r="C81" s="54" t="s">
+      <c r="C81" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="54" t="s">
+      <c r="D81" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="E81" s="54" t="s">
+      <c r="E81" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="F81" s="54" t="s">
+      <c r="F81" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G81" s="54" t="s">
+      <c r="G81" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="H81" s="34"/>
+      <c r="H81" s="33"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="28"/>
-      <c r="B82" s="62">
+      <c r="B82" s="58">
         <v>5</v>
       </c>
-      <c r="C82" s="62" t="s">
+      <c r="C82" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="D82" s="54" t="s">
+      <c r="D82" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="E82" s="62" t="s">
+      <c r="E82" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="F82" s="62" t="s">
+      <c r="F82" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G82" s="62" t="s">
+      <c r="G82" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="H82" s="34"/>
+      <c r="H82" s="33"/>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="28"/>
-      <c r="B83" s="62"/>
-      <c r="C83" s="62"/>
-      <c r="D83" s="54" t="s">
+      <c r="B83" s="58"/>
+      <c r="C83" s="58"/>
+      <c r="D83" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="E83" s="62"/>
-      <c r="F83" s="62"/>
-      <c r="G83" s="62"/>
-      <c r="H83" s="34"/>
+      <c r="E83" s="58"/>
+      <c r="F83" s="58"/>
+      <c r="G83" s="58"/>
+      <c r="H83" s="33"/>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="28"/>
-      <c r="B84" s="62"/>
-      <c r="C84" s="62"/>
-      <c r="D84" s="54" t="s">
+      <c r="B84" s="58"/>
+      <c r="C84" s="58"/>
+      <c r="D84" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62"/>
-      <c r="G84" s="62"/>
-      <c r="H84" s="34"/>
+      <c r="E84" s="58"/>
+      <c r="F84" s="58"/>
+      <c r="G84" s="58"/>
+      <c r="H84" s="33"/>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="28"/>
-      <c r="B85" s="62"/>
-      <c r="C85" s="62"/>
-      <c r="D85" s="54" t="s">
+      <c r="B85" s="58"/>
+      <c r="C85" s="58"/>
+      <c r="D85" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="E85" s="62"/>
-      <c r="F85" s="62"/>
-      <c r="G85" s="62"/>
-      <c r="H85" s="34"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="58"/>
+      <c r="G85" s="58"/>
+      <c r="H85" s="33"/>
     </row>
     <row r="86" spans="1:8" ht="27.6">
       <c r="A86" s="28"/>
-      <c r="B86" s="62"/>
-      <c r="C86" s="62"/>
-      <c r="D86" s="54" t="s">
+      <c r="B86" s="58"/>
+      <c r="C86" s="58"/>
+      <c r="D86" s="41" t="s">
         <v>184</v>
       </c>
-      <c r="E86" s="62"/>
-      <c r="F86" s="62"/>
-      <c r="G86" s="62"/>
-      <c r="H86" s="34"/>
+      <c r="E86" s="58"/>
+      <c r="F86" s="58"/>
+      <c r="G86" s="58"/>
+      <c r="H86" s="33"/>
     </row>
     <row r="87" spans="1:8" ht="69">
       <c r="A87" s="28"/>
-      <c r="B87" s="54">
+      <c r="B87" s="41">
         <v>6</v>
       </c>
-      <c r="C87" s="54" t="s">
+      <c r="C87" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="D87" s="54" t="s">
+      <c r="D87" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="E87" s="54" t="s">
+      <c r="E87" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="F87" s="54" t="s">
+      <c r="F87" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G87" s="54" t="s">
+      <c r="G87" s="41" t="s">
         <v>189</v>
       </c>
-      <c r="H87" s="34"/>
+      <c r="H87" s="33"/>
     </row>
     <row r="88" spans="1:8">
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
+      <c r="B88" s="36"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
     </row>
     <row r="91" spans="1:8">
-      <c r="B91" s="52"/>
-      <c r="C91" s="52"/>
+      <c r="B91" s="39"/>
+      <c r="C91" s="39"/>
     </row>
     <row r="92" spans="1:8" ht="17.399999999999999">
       <c r="A92" s="28"/>
-      <c r="B92" s="71" t="s">
+      <c r="B92" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="C92" s="71"/>
-      <c r="D92" s="34"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="33"/>
     </row>
     <row r="93" spans="1:8">
-      <c r="B93" s="48"/>
-      <c r="C93" s="48"/>
+      <c r="B93" s="36"/>
+      <c r="C93" s="36"/>
     </row>
     <row r="95" spans="1:8">
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="39"/>
     </row>
     <row r="96" spans="1:8" ht="27.6">
       <c r="A96" s="28"/>
-      <c r="B96" s="56" t="s">
+      <c r="B96" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C96" s="56" t="s">
+      <c r="C96" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D96" s="56" t="s">
+      <c r="D96" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="E96" s="56" t="s">
+      <c r="E96" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F96" s="34"/>
+      <c r="F96" s="33"/>
     </row>
     <row r="97" spans="1:8" ht="55.2">
       <c r="A97" s="28"/>
-      <c r="B97" s="54" t="s">
+      <c r="B97" s="41" t="s">
         <v>190</v>
       </c>
-      <c r="C97" s="54" t="s">
+      <c r="C97" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="D97" s="54" t="s">
+      <c r="D97" s="41" t="s">
         <v>192</v>
       </c>
-      <c r="E97" s="61" t="s">
+      <c r="E97" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="F97" s="34"/>
+      <c r="F97" s="33"/>
     </row>
     <row r="98" spans="1:8" ht="41.4">
       <c r="A98" s="28"/>
-      <c r="B98" s="54" t="s">
+      <c r="B98" s="41" t="s">
         <v>193</v>
       </c>
-      <c r="C98" s="54" t="s">
+      <c r="C98" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="D98" s="54" t="s">
+      <c r="D98" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="E98" s="54" t="s">
+      <c r="E98" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="F98" s="34"/>
+      <c r="F98" s="33"/>
     </row>
     <row r="99" spans="1:8" ht="55.2">
       <c r="A99" s="28"/>
-      <c r="B99" s="54" t="s">
+      <c r="B99" s="41" t="s">
         <v>197</v>
       </c>
-      <c r="C99" s="54" t="s">
+      <c r="C99" s="41" t="s">
         <v>198</v>
       </c>
-      <c r="D99" s="54" t="s">
+      <c r="D99" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="E99" s="54" t="s">
+      <c r="E99" s="41" t="s">
         <v>200</v>
       </c>
-      <c r="F99" s="34"/>
+      <c r="F99" s="33"/>
     </row>
     <row r="100" spans="1:8" ht="41.4">
       <c r="A100" s="28"/>
-      <c r="B100" s="54" t="s">
+      <c r="B100" s="41" t="s">
         <v>201</v>
       </c>
-      <c r="C100" s="54" t="s">
+      <c r="C100" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="D100" s="54" t="s">
+      <c r="D100" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="E100" s="54" t="s">
+      <c r="E100" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="F100" s="34"/>
+      <c r="F100" s="33"/>
     </row>
     <row r="101" spans="1:8" ht="41.4">
       <c r="A101" s="28"/>
-      <c r="B101" s="54" t="s">
+      <c r="B101" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="C101" s="54" t="s">
+      <c r="C101" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="D101" s="54" t="s">
+      <c r="D101" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="E101" s="54" t="s">
+      <c r="E101" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="F101" s="34"/>
+      <c r="F101" s="33"/>
     </row>
     <row r="102" spans="1:8" ht="55.2">
       <c r="A102" s="28"/>
-      <c r="B102" s="54" t="s">
+      <c r="B102" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="C102" s="54" t="s">
+      <c r="C102" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="D102" s="54" t="s">
+      <c r="D102" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="E102" s="54" t="s">
+      <c r="E102" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="F102" s="34"/>
+      <c r="F102" s="33"/>
     </row>
     <row r="103" spans="1:8">
-      <c r="B103" s="48"/>
-      <c r="C103" s="48"/>
-      <c r="D103" s="48"/>
-      <c r="E103" s="48"/>
+      <c r="B103" s="36"/>
+      <c r="C103" s="36"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="36"/>
     </row>
     <row r="106" spans="1:8" ht="14.4" thickBot="1"/>
     <row r="107" spans="1:8" ht="17.399999999999999" thickTop="1">
@@ -5342,382 +5747,382 @@
       <c r="C107" s="59"/>
     </row>
     <row r="110" spans="1:8">
-      <c r="B110" s="52"/>
-      <c r="C110" s="52"/>
-      <c r="D110" s="52"/>
-      <c r="E110" s="52"/>
-      <c r="F110" s="52"/>
-      <c r="G110" s="52"/>
+      <c r="B110" s="39"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="39"/>
+      <c r="F110" s="39"/>
+      <c r="G110" s="39"/>
     </row>
     <row r="111" spans="1:8" ht="42" customHeight="1">
       <c r="A111" s="28"/>
-      <c r="B111" s="53" t="s">
+      <c r="B111" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C111" s="53" t="s">
+      <c r="C111" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D111" s="53" t="s">
+      <c r="D111" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="E111" s="53" t="s">
+      <c r="E111" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F111" s="53" t="s">
+      <c r="F111" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="G111" s="53" t="s">
+      <c r="G111" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="H111" s="34"/>
+      <c r="H111" s="33"/>
     </row>
     <row r="112" spans="1:8" ht="42.6" customHeight="1">
       <c r="A112" s="28"/>
-      <c r="B112" s="54">
+      <c r="B112" s="41">
         <v>1</v>
       </c>
-      <c r="C112" s="54" t="s">
+      <c r="C112" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D112" s="61" t="s">
+      <c r="D112" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="E112" s="54" t="s">
+      <c r="E112" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="F112" s="54" t="s">
+      <c r="F112" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G112" s="54" t="s">
+      <c r="G112" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="H112" s="34"/>
+      <c r="H112" s="33"/>
     </row>
     <row r="113" spans="1:8" ht="13.8" customHeight="1">
       <c r="A113" s="28"/>
-      <c r="B113" s="62">
+      <c r="B113" s="58">
         <v>2</v>
       </c>
-      <c r="C113" s="62" t="s">
+      <c r="C113" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D113" s="54" t="s">
+      <c r="D113" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E113" s="62" t="s">
+      <c r="E113" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="F113" s="62" t="s">
+      <c r="F113" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G113" s="62" t="s">
+      <c r="G113" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="H113" s="34"/>
+      <c r="H113" s="33"/>
     </row>
     <row r="114" spans="1:8" ht="23.4" customHeight="1">
       <c r="A114" s="28"/>
-      <c r="B114" s="62"/>
-      <c r="C114" s="62"/>
-      <c r="D114" s="54" t="s">
+      <c r="B114" s="58"/>
+      <c r="C114" s="58"/>
+      <c r="D114" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E114" s="62"/>
-      <c r="F114" s="62"/>
-      <c r="G114" s="62"/>
-      <c r="H114" s="34"/>
+      <c r="E114" s="58"/>
+      <c r="F114" s="58"/>
+      <c r="G114" s="58"/>
+      <c r="H114" s="33"/>
     </row>
     <row r="115" spans="1:8" ht="27.6">
       <c r="A115" s="28"/>
-      <c r="B115" s="54">
+      <c r="B115" s="41">
         <v>3</v>
       </c>
-      <c r="C115" s="54" t="s">
+      <c r="C115" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="D115" s="54" t="s">
+      <c r="D115" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="E115" s="54" t="s">
+      <c r="E115" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="F115" s="54" t="s">
+      <c r="F115" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G115" s="54" t="s">
+      <c r="G115" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="H115" s="34"/>
+      <c r="H115" s="33"/>
     </row>
     <row r="116" spans="1:8" ht="27.6">
       <c r="A116" s="28"/>
-      <c r="B116" s="54">
+      <c r="B116" s="41">
         <v>4</v>
       </c>
-      <c r="C116" s="54" t="s">
+      <c r="C116" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="D116" s="54" t="s">
+      <c r="D116" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="E116" s="54" t="s">
+      <c r="E116" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="F116" s="54" t="s">
+      <c r="F116" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G116" s="54" t="s">
+      <c r="G116" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="H116" s="34"/>
+      <c r="H116" s="33"/>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="28"/>
-      <c r="B117" s="62">
+      <c r="B117" s="58">
         <v>5</v>
       </c>
-      <c r="C117" s="62" t="s">
+      <c r="C117" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="D117" s="78" t="s">
+      <c r="D117" s="61" t="s">
         <v>236</v>
       </c>
-      <c r="E117" s="62" t="s">
+      <c r="E117" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="F117" s="62" t="s">
+      <c r="F117" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G117" s="62" t="s">
+      <c r="G117" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="H117" s="34"/>
+      <c r="H117" s="33"/>
     </row>
     <row r="118" spans="1:8" ht="75.599999999999994" customHeight="1">
       <c r="A118" s="28"/>
-      <c r="B118" s="62"/>
-      <c r="C118" s="62"/>
-      <c r="D118" s="79"/>
-      <c r="E118" s="62"/>
-      <c r="F118" s="62"/>
-      <c r="G118" s="62"/>
-      <c r="H118" s="34"/>
+      <c r="B118" s="58"/>
+      <c r="C118" s="58"/>
+      <c r="D118" s="62"/>
+      <c r="E118" s="58"/>
+      <c r="F118" s="58"/>
+      <c r="G118" s="58"/>
+      <c r="H118" s="33"/>
     </row>
     <row r="119" spans="1:8" ht="27.6">
       <c r="A119" s="28"/>
-      <c r="B119" s="54">
+      <c r="B119" s="41">
         <v>6</v>
       </c>
-      <c r="C119" s="54" t="s">
+      <c r="C119" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="D119" s="54" t="s">
+      <c r="D119" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="E119" s="54" t="s">
+      <c r="E119" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="F119" s="54" t="s">
+      <c r="F119" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G119" s="54" t="s">
+      <c r="G119" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="H119" s="34"/>
+      <c r="H119" s="33"/>
     </row>
     <row r="120" spans="1:8" ht="27.6">
       <c r="A120" s="28"/>
-      <c r="B120" s="54">
+      <c r="B120" s="41">
         <v>7</v>
       </c>
-      <c r="C120" s="54" t="s">
+      <c r="C120" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="D120" s="54" t="s">
+      <c r="D120" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="E120" s="54" t="s">
+      <c r="E120" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="F120" s="54" t="s">
+      <c r="F120" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G120" s="54" t="s">
+      <c r="G120" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="H120" s="34"/>
+      <c r="H120" s="33"/>
     </row>
     <row r="121" spans="1:8" ht="27.6">
       <c r="A121" s="28"/>
-      <c r="B121" s="54">
+      <c r="B121" s="41">
         <v>8</v>
       </c>
-      <c r="C121" s="54" t="s">
+      <c r="C121" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="D121" s="54" t="s">
+      <c r="D121" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="E121" s="54" t="s">
+      <c r="E121" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="F121" s="54" t="s">
+      <c r="F121" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G121" s="54" t="s">
+      <c r="G121" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="H121" s="34"/>
+      <c r="H121" s="33"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="28"/>
-      <c r="B122" s="74"/>
-      <c r="C122" s="74"/>
-      <c r="D122" s="74"/>
-      <c r="E122" s="74"/>
-      <c r="F122" s="74"/>
-      <c r="G122" s="74"/>
-      <c r="H122" s="34"/>
+      <c r="B122" s="53"/>
+      <c r="C122" s="53"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="53"/>
+      <c r="F122" s="53"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="33"/>
     </row>
     <row r="125" spans="1:8">
-      <c r="B125" s="52"/>
-      <c r="C125" s="52"/>
+      <c r="B125" s="39"/>
+      <c r="C125" s="39"/>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="28"/>
-      <c r="B126" s="70" t="s">
+      <c r="B126" s="60" t="s">
         <v>244</v>
       </c>
-      <c r="C126" s="70"/>
-      <c r="D126" s="34"/>
+      <c r="C126" s="60"/>
+      <c r="D126" s="33"/>
     </row>
     <row r="127" spans="1:8">
-      <c r="B127" s="48"/>
-      <c r="C127" s="48"/>
+      <c r="B127" s="36"/>
+      <c r="C127" s="36"/>
     </row>
     <row r="128" spans="1:8">
-      <c r="B128" s="52"/>
-      <c r="C128" s="52"/>
-      <c r="D128" s="52"/>
-      <c r="E128" s="52"/>
+      <c r="B128" s="39"/>
+      <c r="C128" s="39"/>
+      <c r="D128" s="39"/>
+      <c r="E128" s="39"/>
     </row>
     <row r="129" spans="1:8" ht="27.6">
       <c r="A129" s="28"/>
-      <c r="B129" s="56" t="s">
+      <c r="B129" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C129" s="56" t="s">
+      <c r="C129" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="D129" s="56" t="s">
+      <c r="D129" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="E129" s="56" t="s">
+      <c r="E129" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F129" s="34"/>
+      <c r="F129" s="33"/>
     </row>
     <row r="130" spans="1:8" ht="55.2">
       <c r="A130" s="28"/>
-      <c r="B130" s="80" t="s">
+      <c r="B130" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="C130" s="80" t="s">
+      <c r="C130" s="41" t="s">
         <v>191</v>
       </c>
-      <c r="D130" s="80" t="s">
+      <c r="D130" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="E130" s="81" t="s">
+      <c r="E130" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="F130" s="34"/>
+      <c r="F130" s="33"/>
     </row>
     <row r="131" spans="1:8" ht="41.4">
       <c r="A131" s="28"/>
-      <c r="B131" s="80" t="s">
+      <c r="B131" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="C131" s="80" t="s">
+      <c r="C131" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="D131" s="80" t="s">
+      <c r="D131" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="E131" s="80" t="s">
+      <c r="E131" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="F131" s="34"/>
+      <c r="F131" s="33"/>
     </row>
     <row r="132" spans="1:8" ht="55.2">
       <c r="A132" s="28"/>
-      <c r="B132" s="80" t="s">
+      <c r="B132" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="C132" s="80" t="s">
+      <c r="C132" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="D132" s="80" t="s">
+      <c r="D132" s="41" t="s">
         <v>248</v>
       </c>
-      <c r="E132" s="80" t="s">
+      <c r="E132" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="F132" s="34"/>
+      <c r="F132" s="33"/>
     </row>
     <row r="133" spans="1:8" ht="41.4">
       <c r="A133" s="28"/>
-      <c r="B133" s="80" t="s">
+      <c r="B133" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="C133" s="80" t="s">
+      <c r="C133" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="D133" s="80" t="s">
+      <c r="D133" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="E133" s="80" t="s">
+      <c r="E133" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="F133" s="34"/>
+      <c r="F133" s="33"/>
     </row>
     <row r="134" spans="1:8" ht="55.2">
       <c r="A134" s="28"/>
-      <c r="B134" s="80" t="s">
+      <c r="B134" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="C134" s="80" t="s">
+      <c r="C134" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="D134" s="80" t="s">
+      <c r="D134" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="E134" s="80" t="s">
+      <c r="E134" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="F134" s="34"/>
+      <c r="F134" s="33"/>
     </row>
     <row r="135" spans="1:8" ht="55.2">
       <c r="A135" s="28"/>
-      <c r="B135" s="80" t="s">
+      <c r="B135" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="C135" s="80" t="s">
+      <c r="C135" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="D135" s="80" t="s">
+      <c r="D135" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="E135" s="80" t="s">
+      <c r="E135" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="F135" s="34"/>
+      <c r="F135" s="33"/>
     </row>
     <row r="136" spans="1:8">
-      <c r="B136" s="48"/>
-      <c r="C136" s="48"/>
-      <c r="D136" s="48"/>
-      <c r="E136" s="48"/>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
     </row>
     <row r="137" spans="1:8" ht="14.4" thickBot="1"/>
     <row r="138" spans="1:8" ht="17.399999999999999" thickTop="1">
@@ -5727,362 +6132,1405 @@
       <c r="C138" s="59"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="B139" s="52"/>
-      <c r="C139" s="52"/>
-      <c r="D139" s="52"/>
-      <c r="E139" s="52"/>
-      <c r="F139" s="52"/>
-      <c r="G139" s="52"/>
+      <c r="B139" s="39"/>
+      <c r="C139" s="39"/>
+      <c r="D139" s="39"/>
+      <c r="E139" s="39"/>
+      <c r="F139" s="39"/>
+      <c r="G139" s="39"/>
     </row>
     <row r="140" spans="1:8" ht="27.6">
       <c r="A140" s="28"/>
-      <c r="B140" s="56" t="s">
+      <c r="B140" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C140" s="56" t="s">
+      <c r="C140" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="D140" s="56" t="s">
+      <c r="D140" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="E140" s="56" t="s">
+      <c r="E140" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="F140" s="56" t="s">
+      <c r="F140" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="G140" s="56" t="s">
+      <c r="G140" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="H140" s="34"/>
+      <c r="H140" s="33"/>
     </row>
     <row r="141" spans="1:8" ht="27.6">
       <c r="A141" s="28"/>
-      <c r="B141" s="54">
+      <c r="B141" s="41">
         <v>1</v>
       </c>
-      <c r="C141" s="54" t="s">
+      <c r="C141" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D141" s="61" t="s">
+      <c r="D141" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="E141" s="54" t="s">
+      <c r="E141" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="F141" s="54" t="s">
+      <c r="F141" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G141" s="54" t="s">
+      <c r="G141" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="H141" s="34"/>
+      <c r="H141" s="33"/>
     </row>
     <row r="142" spans="1:8" ht="13.8" customHeight="1">
       <c r="A142" s="28"/>
-      <c r="B142" s="62">
+      <c r="B142" s="58">
         <v>2</v>
       </c>
-      <c r="C142" s="62" t="s">
+      <c r="C142" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="D142" s="54" t="s">
+      <c r="D142" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E142" s="62" t="s">
+      <c r="E142" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="F142" s="62" t="s">
+      <c r="F142" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G142" s="62" t="s">
+      <c r="G142" s="58" t="s">
         <v>167</v>
       </c>
-      <c r="H142" s="34"/>
+      <c r="H142" s="33"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="28"/>
-      <c r="B143" s="62"/>
-      <c r="C143" s="62"/>
-      <c r="D143" s="54" t="s">
+      <c r="B143" s="58"/>
+      <c r="C143" s="58"/>
+      <c r="D143" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="E143" s="62"/>
-      <c r="F143" s="62"/>
-      <c r="G143" s="62"/>
-      <c r="H143" s="34"/>
+      <c r="E143" s="58"/>
+      <c r="F143" s="58"/>
+      <c r="G143" s="58"/>
+      <c r="H143" s="33"/>
     </row>
     <row r="144" spans="1:8" ht="27.6">
       <c r="A144" s="28"/>
-      <c r="B144" s="54">
+      <c r="B144" s="41">
         <v>3</v>
       </c>
-      <c r="C144" s="54" t="s">
+      <c r="C144" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="D144" s="54" t="s">
+      <c r="D144" s="41" t="s">
         <v>260</v>
       </c>
-      <c r="E144" s="54" t="s">
+      <c r="E144" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="F144" s="54" t="s">
+      <c r="F144" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G144" s="54" t="s">
+      <c r="G144" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="H144" s="34"/>
+      <c r="H144" s="33"/>
     </row>
     <row r="145" spans="1:8" ht="27.6">
       <c r="A145" s="28"/>
-      <c r="B145" s="54">
+      <c r="B145" s="41">
         <v>4</v>
       </c>
-      <c r="C145" s="54" t="s">
+      <c r="C145" s="41" t="s">
         <v>263</v>
       </c>
-      <c r="D145" s="54" t="s">
+      <c r="D145" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="E145" s="54" t="s">
+      <c r="E145" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="F145" s="54" t="s">
+      <c r="F145" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G145" s="54" t="s">
+      <c r="G145" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="H145" s="34"/>
+      <c r="H145" s="33"/>
     </row>
     <row r="146" spans="1:8" ht="27.6">
       <c r="A146" s="28"/>
-      <c r="B146" s="62">
+      <c r="B146" s="58">
         <v>5</v>
       </c>
-      <c r="C146" s="62" t="s">
+      <c r="C146" s="58" t="s">
         <v>266</v>
       </c>
-      <c r="D146" s="54" t="s">
+      <c r="D146" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="E146" s="62" t="s">
+      <c r="E146" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="F146" s="62" t="s">
+      <c r="F146" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G146" s="62" t="s">
+      <c r="G146" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="H146" s="34"/>
+      <c r="H146" s="33"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="28"/>
-      <c r="B147" s="62"/>
-      <c r="C147" s="62"/>
-      <c r="D147" s="54" t="s">
+      <c r="B147" s="58"/>
+      <c r="C147" s="58"/>
+      <c r="D147" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="E147" s="62"/>
-      <c r="F147" s="62"/>
-      <c r="G147" s="62"/>
-      <c r="H147" s="34"/>
+      <c r="E147" s="58"/>
+      <c r="F147" s="58"/>
+      <c r="G147" s="58"/>
+      <c r="H147" s="33"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="28"/>
-      <c r="B148" s="62"/>
-      <c r="C148" s="62"/>
-      <c r="D148" s="54" t="s">
+      <c r="B148" s="58"/>
+      <c r="C148" s="58"/>
+      <c r="D148" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="E148" s="62"/>
-      <c r="F148" s="62"/>
-      <c r="G148" s="62"/>
-      <c r="H148" s="34"/>
+      <c r="E148" s="58"/>
+      <c r="F148" s="58"/>
+      <c r="G148" s="58"/>
+      <c r="H148" s="33"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="28"/>
-      <c r="B149" s="62"/>
-      <c r="C149" s="62"/>
-      <c r="D149" s="54" t="s">
+      <c r="B149" s="58"/>
+      <c r="C149" s="58"/>
+      <c r="D149" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="E149" s="62"/>
-      <c r="F149" s="62"/>
-      <c r="G149" s="62"/>
-      <c r="H149" s="34"/>
+      <c r="E149" s="58"/>
+      <c r="F149" s="58"/>
+      <c r="G149" s="58"/>
+      <c r="H149" s="33"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="28"/>
-      <c r="B150" s="62">
+      <c r="B150" s="58">
         <v>6</v>
       </c>
-      <c r="C150" s="62" t="s">
+      <c r="C150" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="D150" s="54" t="s">
+      <c r="D150" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="E150" s="62" t="s">
+      <c r="E150" s="58" t="s">
         <v>277</v>
       </c>
-      <c r="F150" s="62" t="s">
+      <c r="F150" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G150" s="62" t="s">
+      <c r="G150" s="58" t="s">
         <v>278</v>
       </c>
-      <c r="H150" s="34"/>
+      <c r="H150" s="33"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="28"/>
-      <c r="B151" s="62"/>
-      <c r="C151" s="62"/>
-      <c r="D151" s="54" t="s">
+      <c r="B151" s="58"/>
+      <c r="C151" s="58"/>
+      <c r="D151" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="E151" s="62"/>
-      <c r="F151" s="62"/>
-      <c r="G151" s="62"/>
-      <c r="H151" s="34"/>
+      <c r="E151" s="58"/>
+      <c r="F151" s="58"/>
+      <c r="G151" s="58"/>
+      <c r="H151" s="33"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="28"/>
-      <c r="B152" s="62"/>
-      <c r="C152" s="62"/>
-      <c r="D152" s="54" t="s">
+      <c r="B152" s="58"/>
+      <c r="C152" s="58"/>
+      <c r="D152" s="41" t="s">
         <v>275</v>
       </c>
-      <c r="E152" s="62"/>
-      <c r="F152" s="62"/>
-      <c r="G152" s="62"/>
-      <c r="H152" s="34"/>
+      <c r="E152" s="58"/>
+      <c r="F152" s="58"/>
+      <c r="G152" s="58"/>
+      <c r="H152" s="33"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="28"/>
-      <c r="B153" s="62"/>
-      <c r="C153" s="62"/>
-      <c r="D153" s="54" t="s">
+      <c r="B153" s="58"/>
+      <c r="C153" s="58"/>
+      <c r="D153" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="E153" s="62"/>
-      <c r="F153" s="62"/>
-      <c r="G153" s="62"/>
-      <c r="H153" s="34"/>
+      <c r="E153" s="58"/>
+      <c r="F153" s="58"/>
+      <c r="G153" s="58"/>
+      <c r="H153" s="33"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="28"/>
-      <c r="B154" s="62">
+      <c r="B154" s="58">
         <v>7</v>
       </c>
-      <c r="C154" s="62" t="s">
+      <c r="C154" s="58" t="s">
         <v>279</v>
       </c>
-      <c r="D154" s="54" t="s">
+      <c r="D154" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="E154" s="62" t="s">
+      <c r="E154" s="58" t="s">
         <v>284</v>
       </c>
-      <c r="F154" s="62" t="s">
+      <c r="F154" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="G154" s="62" t="s">
+      <c r="G154" s="58" t="s">
         <v>285</v>
       </c>
-      <c r="H154" s="34"/>
+      <c r="H154" s="33"/>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="28"/>
-      <c r="B155" s="62"/>
-      <c r="C155" s="62"/>
-      <c r="D155" s="54" t="s">
+      <c r="B155" s="58"/>
+      <c r="C155" s="58"/>
+      <c r="D155" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="E155" s="62"/>
-      <c r="F155" s="62"/>
-      <c r="G155" s="62"/>
-      <c r="H155" s="34"/>
+      <c r="E155" s="58"/>
+      <c r="F155" s="58"/>
+      <c r="G155" s="58"/>
+      <c r="H155" s="33"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="28"/>
-      <c r="B156" s="62"/>
-      <c r="C156" s="62"/>
-      <c r="D156" s="54" t="s">
+      <c r="B156" s="58"/>
+      <c r="C156" s="58"/>
+      <c r="D156" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="E156" s="62"/>
-      <c r="F156" s="62"/>
-      <c r="G156" s="62"/>
-      <c r="H156" s="34"/>
+      <c r="E156" s="58"/>
+      <c r="F156" s="58"/>
+      <c r="G156" s="58"/>
+      <c r="H156" s="33"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="28"/>
-      <c r="B157" s="62"/>
-      <c r="C157" s="62"/>
-      <c r="D157" s="54" t="s">
+      <c r="B157" s="58"/>
+      <c r="C157" s="58"/>
+      <c r="D157" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="E157" s="62"/>
-      <c r="F157" s="62"/>
-      <c r="G157" s="62"/>
-      <c r="H157" s="34"/>
+      <c r="E157" s="58"/>
+      <c r="F157" s="58"/>
+      <c r="G157" s="58"/>
+      <c r="H157" s="33"/>
     </row>
     <row r="158" spans="1:8" ht="27.6">
       <c r="A158" s="28"/>
-      <c r="B158" s="54">
+      <c r="B158" s="41">
         <v>8</v>
       </c>
-      <c r="C158" s="54" t="s">
+      <c r="C158" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="D158" s="54" t="s">
+      <c r="D158" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="E158" s="54" t="s">
+      <c r="E158" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="F158" s="54" t="s">
+      <c r="F158" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="G158" s="54" t="s">
+      <c r="G158" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="H158" s="34"/>
+      <c r="H158" s="33"/>
     </row>
     <row r="159" spans="1:8">
-      <c r="B159" s="48"/>
-      <c r="C159" s="48"/>
-      <c r="D159" s="48"/>
-      <c r="E159" s="48"/>
-      <c r="F159" s="48"/>
-      <c r="G159" s="48"/>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+      <c r="G159" s="36"/>
+    </row>
+    <row r="163" spans="2:8" ht="15.6">
+      <c r="B163" s="84" t="s">
+        <v>291</v>
+      </c>
+      <c r="C163" s="85"/>
+      <c r="D163" s="85"/>
+      <c r="E163" s="85"/>
+      <c r="F163" s="85"/>
+      <c r="G163" s="85"/>
+      <c r="H163"/>
+    </row>
+    <row r="164" spans="2:8" ht="15.6">
+      <c r="B164" s="86"/>
+      <c r="C164" s="85"/>
+      <c r="D164" s="85"/>
+      <c r="E164" s="85"/>
+      <c r="F164" s="85"/>
+      <c r="G164" s="85"/>
+      <c r="H164"/>
+    </row>
+    <row r="165" spans="2:8" ht="51" customHeight="1">
+      <c r="B165" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C165" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D165" s="88" t="s">
+        <v>293</v>
+      </c>
+      <c r="E165" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F165" s="85"/>
+      <c r="G165" s="85"/>
+      <c r="H165"/>
+    </row>
+    <row r="166" spans="2:8" ht="36.6" customHeight="1">
+      <c r="B166" s="87" t="s">
+        <v>294</v>
+      </c>
+      <c r="C166" s="87" t="s">
+        <v>295</v>
+      </c>
+      <c r="D166" s="87" t="s">
+        <v>296</v>
+      </c>
+      <c r="E166" s="87" t="s">
+        <v>297</v>
+      </c>
+      <c r="F166" s="85"/>
+      <c r="G166" s="85"/>
+      <c r="H166"/>
+    </row>
+    <row r="167" spans="2:8" ht="15">
+      <c r="B167" s="87" t="s">
+        <v>298</v>
+      </c>
+      <c r="C167" s="87" t="s">
+        <v>299</v>
+      </c>
+      <c r="D167" s="87" t="s">
+        <v>300</v>
+      </c>
+      <c r="E167" s="87" t="s">
+        <v>301</v>
+      </c>
+      <c r="F167" s="85"/>
+      <c r="G167" s="85"/>
+      <c r="H167"/>
+    </row>
+    <row r="168" spans="2:8" ht="15">
+      <c r="B168" s="87" t="s">
+        <v>302</v>
+      </c>
+      <c r="C168" s="87" t="s">
+        <v>303</v>
+      </c>
+      <c r="D168" s="87" t="s">
+        <v>304</v>
+      </c>
+      <c r="E168" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="F168" s="85"/>
+      <c r="G168" s="85"/>
+      <c r="H168"/>
+    </row>
+    <row r="169" spans="2:8" ht="15">
+      <c r="B169" s="87" t="s">
+        <v>306</v>
+      </c>
+      <c r="C169" s="87" t="s">
+        <v>307</v>
+      </c>
+      <c r="D169" s="87" t="s">
+        <v>308</v>
+      </c>
+      <c r="E169" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="F169" s="85"/>
+      <c r="G169" s="85"/>
+      <c r="H169"/>
+    </row>
+    <row r="170" spans="2:8" ht="15">
+      <c r="B170" s="87" t="s">
+        <v>309</v>
+      </c>
+      <c r="C170" s="87" t="s">
+        <v>310</v>
+      </c>
+      <c r="D170" s="87" t="s">
+        <v>311</v>
+      </c>
+      <c r="E170" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="F170" s="85"/>
+      <c r="G170" s="85"/>
+      <c r="H170"/>
+    </row>
+    <row r="171" spans="2:8" ht="15">
+      <c r="B171" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="C171" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="D171" s="87" t="s">
+        <v>314</v>
+      </c>
+      <c r="E171" s="87" t="s">
+        <v>315</v>
+      </c>
+      <c r="F171" s="85"/>
+      <c r="G171" s="85"/>
+      <c r="H171"/>
+    </row>
+    <row r="172" spans="2:8" ht="15">
+      <c r="B172" s="85"/>
+      <c r="C172" s="85"/>
+      <c r="D172" s="85"/>
+      <c r="E172" s="85"/>
+      <c r="F172" s="85"/>
+      <c r="G172" s="85"/>
+      <c r="H172"/>
+    </row>
+    <row r="173" spans="2:8" ht="15.6">
+      <c r="B173" s="84" t="s">
+        <v>316</v>
+      </c>
+      <c r="C173" s="85"/>
+      <c r="D173" s="85"/>
+      <c r="E173" s="85"/>
+      <c r="F173" s="85"/>
+      <c r="G173" s="85"/>
+      <c r="H173"/>
+    </row>
+    <row r="174" spans="2:8" ht="15.6">
+      <c r="B174" s="85"/>
+      <c r="C174" s="86"/>
+      <c r="D174" s="86"/>
+      <c r="E174" s="86"/>
+      <c r="F174" s="85"/>
+      <c r="G174" s="85"/>
+    </row>
+    <row r="175" spans="2:8" ht="64.8" customHeight="1">
+      <c r="B175" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C175" s="88" t="s">
+        <v>293</v>
+      </c>
+      <c r="D175" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="E175" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F175" s="88" t="s">
+        <v>62</v>
+      </c>
+      <c r="G175" s="88" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="176" spans="2:8" ht="15">
+      <c r="B176" s="87">
+        <v>1</v>
+      </c>
+      <c r="C176" s="87" t="s">
+        <v>317</v>
+      </c>
+      <c r="D176" s="87" t="s">
+        <v>318</v>
+      </c>
+      <c r="E176" s="87" t="s">
+        <v>319</v>
+      </c>
+      <c r="F176" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G176" s="87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="177" spans="2:7" ht="15">
+      <c r="B177" s="87">
+        <v>2</v>
+      </c>
+      <c r="C177" s="87" t="s">
+        <v>321</v>
+      </c>
+      <c r="D177" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="E177" s="87" t="s">
+        <v>323</v>
+      </c>
+      <c r="F177" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G177" s="87" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="178" spans="2:7" ht="15">
+      <c r="B178" s="87">
+        <v>3</v>
+      </c>
+      <c r="C178" s="87" t="s">
+        <v>325</v>
+      </c>
+      <c r="D178" s="87" t="s">
+        <v>326</v>
+      </c>
+      <c r="E178" s="87" t="s">
+        <v>327</v>
+      </c>
+      <c r="F178" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G178" s="87" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="179" spans="2:7" ht="15">
+      <c r="B179" s="87">
+        <v>4</v>
+      </c>
+      <c r="C179" s="87" t="s">
+        <v>329</v>
+      </c>
+      <c r="D179" s="87" t="s">
+        <v>330</v>
+      </c>
+      <c r="E179" s="87" t="s">
+        <v>331</v>
+      </c>
+      <c r="F179" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G179" s="87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="180" spans="2:7" ht="15">
+      <c r="B180" s="87">
+        <v>5</v>
+      </c>
+      <c r="C180" s="87" t="s">
+        <v>332</v>
+      </c>
+      <c r="D180" s="87" t="s">
+        <v>333</v>
+      </c>
+      <c r="E180" s="87" t="s">
+        <v>334</v>
+      </c>
+      <c r="F180" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G180" s="87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7" ht="15">
+      <c r="B181" s="85"/>
+      <c r="C181" s="85"/>
+      <c r="D181" s="85"/>
+      <c r="E181" s="85"/>
+      <c r="F181" s="85"/>
+      <c r="G181" s="85"/>
+    </row>
+    <row r="182" spans="2:7" ht="15.6">
+      <c r="B182" s="84" t="s">
+        <v>335</v>
+      </c>
+      <c r="C182" s="86"/>
+      <c r="D182" s="86"/>
+      <c r="E182" s="86"/>
+      <c r="F182" s="86"/>
+      <c r="G182" s="86"/>
+    </row>
+    <row r="183" spans="2:7" ht="15.6">
+      <c r="B183" s="86"/>
+      <c r="C183" s="86"/>
+      <c r="D183" s="86"/>
+      <c r="E183" s="86"/>
+      <c r="F183" s="86"/>
+      <c r="G183" s="86"/>
+    </row>
+    <row r="184" spans="2:7" ht="48" customHeight="1">
+      <c r="B184" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C184" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D184" s="88" t="s">
+        <v>293</v>
+      </c>
+      <c r="E184" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F184" s="86"/>
+      <c r="G184" s="86"/>
+    </row>
+    <row r="185" spans="2:7" ht="15">
+      <c r="B185" s="87" t="s">
+        <v>336</v>
+      </c>
+      <c r="C185" s="87" t="s">
+        <v>321</v>
+      </c>
+      <c r="D185" s="87" t="s">
+        <v>337</v>
+      </c>
+      <c r="E185" s="87" t="s">
+        <v>338</v>
+      </c>
+      <c r="F185" s="85"/>
+      <c r="G185" s="85"/>
+    </row>
+    <row r="186" spans="2:7" ht="15">
+      <c r="B186" s="87" t="s">
+        <v>339</v>
+      </c>
+      <c r="C186" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="D186" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="E186" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="F186" s="85"/>
+      <c r="G186" s="85"/>
+    </row>
+    <row r="187" spans="2:7" ht="15">
+      <c r="B187" s="87" t="s">
+        <v>342</v>
+      </c>
+      <c r="C187" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="D187" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="E187" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="F187" s="85"/>
+      <c r="G187" s="85"/>
+    </row>
+    <row r="188" spans="2:7" ht="15">
+      <c r="B188" s="87" t="s">
+        <v>344</v>
+      </c>
+      <c r="C188" s="87" t="s">
+        <v>345</v>
+      </c>
+      <c r="D188" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="E188" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="F188" s="85"/>
+      <c r="G188" s="85"/>
+    </row>
+    <row r="189" spans="2:7" ht="15">
+      <c r="B189" s="87" t="s">
+        <v>346</v>
+      </c>
+      <c r="C189" s="87" t="s">
+        <v>347</v>
+      </c>
+      <c r="D189" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="E189" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="F189" s="85"/>
+      <c r="G189" s="85"/>
+    </row>
+    <row r="190" spans="2:7" ht="15">
+      <c r="B190" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="C190" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="D190" s="87" t="s">
+        <v>352</v>
+      </c>
+      <c r="E190" s="87" t="s">
+        <v>353</v>
+      </c>
+      <c r="F190" s="85"/>
+      <c r="G190" s="85"/>
+    </row>
+    <row r="191" spans="2:7" ht="15">
+      <c r="B191" s="85"/>
+      <c r="C191" s="85"/>
+      <c r="D191" s="85"/>
+      <c r="E191" s="85"/>
+      <c r="F191" s="85"/>
+      <c r="G191" s="85"/>
+    </row>
+    <row r="192" spans="2:7" ht="15.6">
+      <c r="B192" s="84" t="s">
+        <v>354</v>
+      </c>
+      <c r="C192" s="86"/>
+      <c r="D192" s="86"/>
+      <c r="E192" s="86"/>
+      <c r="F192" s="86"/>
+      <c r="G192" s="86"/>
+    </row>
+    <row r="193" spans="2:7" ht="48.6" customHeight="1">
+      <c r="B193" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C193" s="88" t="s">
+        <v>293</v>
+      </c>
+      <c r="D193" s="88" t="s">
+        <v>28</v>
+      </c>
+      <c r="E193" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F193" s="88" t="s">
+        <v>62</v>
+      </c>
+      <c r="G193" s="88" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="194" spans="2:7" ht="15">
+      <c r="B194" s="87">
+        <v>1</v>
+      </c>
+      <c r="C194" s="87" t="s">
+        <v>355</v>
+      </c>
+      <c r="D194" s="87" t="s">
+        <v>356</v>
+      </c>
+      <c r="E194" s="87" t="s">
+        <v>357</v>
+      </c>
+      <c r="F194" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G194" s="87" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7" ht="15">
+      <c r="B195" s="87">
+        <v>2</v>
+      </c>
+      <c r="C195" s="87" t="s">
+        <v>359</v>
+      </c>
+      <c r="D195" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="E195" s="87" t="s">
+        <v>360</v>
+      </c>
+      <c r="F195" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G195" s="87" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7" ht="15">
+      <c r="B196" s="87">
+        <v>3</v>
+      </c>
+      <c r="C196" s="87" t="s">
+        <v>361</v>
+      </c>
+      <c r="D196" s="87" t="s">
+        <v>362</v>
+      </c>
+      <c r="E196" s="87" t="s">
+        <v>327</v>
+      </c>
+      <c r="F196" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G196" s="87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7" ht="15">
+      <c r="B197" s="87">
+        <v>4</v>
+      </c>
+      <c r="C197" s="87" t="s">
+        <v>363</v>
+      </c>
+      <c r="D197" s="87" t="s">
+        <v>364</v>
+      </c>
+      <c r="E197" s="87" t="s">
+        <v>365</v>
+      </c>
+      <c r="F197" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G197" s="87" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="198" spans="2:7" ht="15">
+      <c r="B198" s="87">
+        <v>5</v>
+      </c>
+      <c r="C198" s="87" t="s">
+        <v>366</v>
+      </c>
+      <c r="D198" s="87" t="s">
+        <v>362</v>
+      </c>
+      <c r="E198" s="87" t="s">
+        <v>367</v>
+      </c>
+      <c r="F198" s="87" t="s">
+        <v>116</v>
+      </c>
+      <c r="G198" s="87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" ht="15">
+      <c r="B199" s="85"/>
+      <c r="C199" s="85"/>
+      <c r="D199" s="85"/>
+      <c r="E199" s="85"/>
+      <c r="F199" s="85"/>
+      <c r="G199" s="85"/>
+    </row>
+    <row r="200" spans="2:7" ht="15.6">
+      <c r="B200" s="90" t="s">
+        <v>368</v>
+      </c>
+      <c r="C200" s="89"/>
+      <c r="D200" s="86"/>
+      <c r="E200" s="86"/>
+      <c r="F200" s="86"/>
+      <c r="G200" s="86"/>
+    </row>
+    <row r="201" spans="2:7" ht="15.6">
+      <c r="B201" s="86"/>
+      <c r="C201" s="86"/>
+      <c r="D201" s="86"/>
+      <c r="E201" s="86"/>
+      <c r="F201" s="86"/>
+      <c r="G201" s="86"/>
+    </row>
+    <row r="202" spans="2:7" ht="57.6" customHeight="1">
+      <c r="B202" s="88" t="s">
+        <v>292</v>
+      </c>
+      <c r="C202" s="88" t="s">
+        <v>23</v>
+      </c>
+      <c r="D202" s="88" t="s">
+        <v>293</v>
+      </c>
+      <c r="E202" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="F202" s="86"/>
+      <c r="G202" s="86"/>
+    </row>
+    <row r="203" spans="2:7" ht="15">
+      <c r="B203" s="87" t="s">
+        <v>369</v>
+      </c>
+      <c r="C203" s="87" t="s">
+        <v>321</v>
+      </c>
+      <c r="D203" s="87" t="s">
+        <v>337</v>
+      </c>
+      <c r="E203" s="87" t="s">
+        <v>370</v>
+      </c>
+      <c r="F203" s="85"/>
+      <c r="G203" s="85"/>
+    </row>
+    <row r="204" spans="2:7" ht="15">
+      <c r="B204" s="87" t="s">
+        <v>371</v>
+      </c>
+      <c r="C204" s="87" t="s">
+        <v>372</v>
+      </c>
+      <c r="D204" s="87" t="s">
+        <v>373</v>
+      </c>
+      <c r="E204" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="F204" s="85"/>
+      <c r="G204" s="85"/>
+    </row>
+    <row r="205" spans="2:7" ht="15">
+      <c r="B205" s="87" t="s">
+        <v>374</v>
+      </c>
+      <c r="C205" s="87" t="s">
+        <v>375</v>
+      </c>
+      <c r="D205" s="87" t="s">
+        <v>376</v>
+      </c>
+      <c r="E205" s="87" t="s">
+        <v>377</v>
+      </c>
+      <c r="F205" s="85"/>
+      <c r="G205" s="85"/>
+    </row>
+    <row r="206" spans="2:7" ht="15">
+      <c r="B206" s="87" t="s">
+        <v>378</v>
+      </c>
+      <c r="C206" s="87" t="s">
+        <v>379</v>
+      </c>
+      <c r="D206" s="87" t="s">
+        <v>380</v>
+      </c>
+      <c r="E206" s="87" t="s">
+        <v>381</v>
+      </c>
+      <c r="F206" s="85"/>
+      <c r="G206" s="85"/>
+    </row>
+    <row r="207" spans="2:7" ht="15">
+      <c r="B207" s="85"/>
+      <c r="C207" s="85"/>
+      <c r="D207" s="85"/>
+      <c r="E207" s="85"/>
+      <c r="F207" s="85"/>
+      <c r="G207" s="85"/>
+    </row>
+    <row r="208" spans="2:7" ht="15.6">
+      <c r="B208" s="84" t="s">
+        <v>382</v>
+      </c>
+      <c r="C208" s="85"/>
+      <c r="D208" s="85"/>
+      <c r="E208" s="85"/>
+      <c r="F208" s="85"/>
+      <c r="G208" s="85"/>
+    </row>
+    <row r="209" spans="2:7" ht="15.6">
+      <c r="B209" s="85"/>
+      <c r="C209" s="86"/>
+      <c r="D209" s="86"/>
+      <c r="E209" s="86"/>
+      <c r="F209" s="86"/>
+      <c r="G209" s="86"/>
+    </row>
+    <row r="210" spans="2:7" ht="60.6" customHeight="1">
+      <c r="B210" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C210" s="91" t="s">
+        <v>293</v>
+      </c>
+      <c r="D210" s="91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E210" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F210" s="91" t="s">
+        <v>62</v>
+      </c>
+      <c r="G210" s="91" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7">
+      <c r="B211" s="53">
+        <v>1</v>
+      </c>
+      <c r="C211" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D211" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="E211" s="53" t="s">
+        <v>360</v>
+      </c>
+      <c r="F211" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G211" s="53" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7">
+      <c r="B212" s="53">
+        <v>2</v>
+      </c>
+      <c r="C212" s="53" t="s">
+        <v>383</v>
+      </c>
+      <c r="D212" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="E212" s="53" t="s">
+        <v>384</v>
+      </c>
+      <c r="F212" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G212" s="53" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7">
+      <c r="B213" s="53">
+        <v>3</v>
+      </c>
+      <c r="C213" s="53" t="s">
+        <v>376</v>
+      </c>
+      <c r="D213" s="53" t="s">
+        <v>385</v>
+      </c>
+      <c r="E213" s="53" t="s">
+        <v>386</v>
+      </c>
+      <c r="F213" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G213" s="53" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7">
+      <c r="B214" s="53">
+        <v>4</v>
+      </c>
+      <c r="C214" s="53" t="s">
+        <v>388</v>
+      </c>
+      <c r="D214" s="53" t="s">
+        <v>389</v>
+      </c>
+      <c r="E214" s="53" t="s">
+        <v>390</v>
+      </c>
+      <c r="F214" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G214" s="53" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7">
+      <c r="B215"/>
+      <c r="C215"/>
+      <c r="D215"/>
+      <c r="E215"/>
+      <c r="F215"/>
+      <c r="G215"/>
+    </row>
+    <row r="216" spans="2:7" ht="14.4">
+      <c r="B216" s="81" t="s">
+        <v>391</v>
+      </c>
+      <c r="C216"/>
+      <c r="D216"/>
+      <c r="E216"/>
+      <c r="F216"/>
+      <c r="G216"/>
+    </row>
+    <row r="217" spans="2:7" ht="14.4">
+      <c r="B217"/>
+      <c r="C217" s="82"/>
+      <c r="D217" s="82"/>
+      <c r="E217" s="82"/>
+      <c r="F217" s="82"/>
+      <c r="G217" s="82"/>
+    </row>
+    <row r="218" spans="2:7" ht="46.8" customHeight="1">
+      <c r="B218" s="91" t="s">
+        <v>292</v>
+      </c>
+      <c r="C218" s="91" t="s">
+        <v>23</v>
+      </c>
+      <c r="D218" s="91" t="s">
+        <v>293</v>
+      </c>
+      <c r="E218" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="F218" s="82"/>
+      <c r="G218" s="82"/>
+    </row>
+    <row r="219" spans="2:7">
+      <c r="B219" s="53" t="s">
+        <v>392</v>
+      </c>
+      <c r="C219" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D219" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="E219" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="F219"/>
+      <c r="G219"/>
+    </row>
+    <row r="220" spans="2:7">
+      <c r="B220" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="C220" s="53" t="s">
+        <v>394</v>
+      </c>
+      <c r="D220" s="53" t="s">
+        <v>395</v>
+      </c>
+      <c r="E220" s="53" t="s">
+        <v>349</v>
+      </c>
+      <c r="F220"/>
+      <c r="G220"/>
+    </row>
+    <row r="221" spans="2:7">
+      <c r="B221" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="C221" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="D221" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="E221" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="F221"/>
+      <c r="G221"/>
+    </row>
+    <row r="222" spans="2:7">
+      <c r="B222" s="53" t="s">
+        <v>399</v>
+      </c>
+      <c r="C222" s="53" t="s">
+        <v>400</v>
+      </c>
+      <c r="D222" s="53" t="s">
+        <v>401</v>
+      </c>
+      <c r="E222" s="53" t="s">
+        <v>353</v>
+      </c>
+      <c r="F222"/>
+      <c r="G222"/>
+    </row>
+    <row r="223" spans="2:7">
+      <c r="B223"/>
+      <c r="C223"/>
+      <c r="D223"/>
+      <c r="E223"/>
+      <c r="F223"/>
+      <c r="G223"/>
+    </row>
+    <row r="224" spans="2:7" ht="14.4">
+      <c r="B224" s="81" t="s">
+        <v>402</v>
+      </c>
+      <c r="C224"/>
+      <c r="D224"/>
+      <c r="E224"/>
+      <c r="F224"/>
+      <c r="G224"/>
+    </row>
+    <row r="225" spans="2:7" ht="14.4">
+      <c r="B225"/>
+      <c r="C225" s="82"/>
+      <c r="D225" s="82"/>
+      <c r="E225" s="82"/>
+      <c r="F225" s="82"/>
+      <c r="G225" s="82"/>
+    </row>
+    <row r="226" spans="2:7" ht="49.8" customHeight="1">
+      <c r="B226" s="83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C226" s="83" t="s">
+        <v>293</v>
+      </c>
+      <c r="D226" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="E226" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F226" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="G226" s="83" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227" spans="2:7">
+      <c r="B227" s="53">
+        <v>1</v>
+      </c>
+      <c r="C227" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D227" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="E227" s="53" t="s">
+        <v>360</v>
+      </c>
+      <c r="F227" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G227" s="53" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="228" spans="2:7">
+      <c r="B228" s="53">
+        <v>2</v>
+      </c>
+      <c r="C228" s="53" t="s">
+        <v>403</v>
+      </c>
+      <c r="D228" s="53" t="s">
+        <v>362</v>
+      </c>
+      <c r="E228" s="53" t="s">
+        <v>384</v>
+      </c>
+      <c r="F228" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G228" s="53" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="229" spans="2:7">
+      <c r="B229" s="53">
+        <v>3</v>
+      </c>
+      <c r="C229" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="D229" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="E229" s="53" t="s">
+        <v>365</v>
+      </c>
+      <c r="F229" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G229" s="53" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="230" spans="2:7">
+      <c r="B230" s="53">
+        <v>4</v>
+      </c>
+      <c r="C230" s="53" t="s">
+        <v>405</v>
+      </c>
+      <c r="D230" s="53" t="s">
+        <v>406</v>
+      </c>
+      <c r="E230" s="53" t="s">
+        <v>407</v>
+      </c>
+      <c r="F230" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="G230" s="53" t="s">
+        <v>320</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="C154:C157"/>
-    <mergeCell ref="E154:E157"/>
-    <mergeCell ref="F154:F157"/>
-    <mergeCell ref="G154:G157"/>
-    <mergeCell ref="B138:C138"/>
-    <mergeCell ref="B146:B149"/>
-    <mergeCell ref="C146:C149"/>
-    <mergeCell ref="E146:E149"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="G146:G149"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="C150:C153"/>
-    <mergeCell ref="E150:E153"/>
-    <mergeCell ref="F150:F153"/>
-    <mergeCell ref="G150:G153"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="F142:F143"/>
+  <mergeCells count="68">
+    <mergeCell ref="B200:C200"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B13:G15"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="E82:E86"/>
+    <mergeCell ref="F82:F86"/>
+    <mergeCell ref="G82:G86"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B113:B114"/>
+    <mergeCell ref="C113:C114"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
     <mergeCell ref="G142:G143"/>
     <mergeCell ref="F113:F114"/>
     <mergeCell ref="G113:G114"/>
@@ -6092,43 +7540,28 @@
     <mergeCell ref="F117:F118"/>
     <mergeCell ref="G117:G118"/>
     <mergeCell ref="D117:D118"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="C113:C114"/>
     <mergeCell ref="E113:E114"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="F82:F86"/>
-    <mergeCell ref="G82:G86"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B13:G15"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="F142:F143"/>
+    <mergeCell ref="G146:G149"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="C150:C153"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="F150:F153"/>
+    <mergeCell ref="G150:G153"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="C146:C149"/>
+    <mergeCell ref="E146:E149"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="E154:E157"/>
+    <mergeCell ref="F154:F157"/>
+    <mergeCell ref="G154:G157"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D31" r:id="rId1" display="http://localhost:5173/" xr:uid="{274F3558-C2BD-487B-9443-74A285BBE3F3}"/>
